--- a/etf_holdings/2026-09-29_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:22</t>
+          <t>2026-09-29 01:00:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:24</t>
+          <t>2026-09-29 01:00:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:27</t>
+          <t>2026-09-29 01:00:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:28</t>
+          <t>2026-09-29 01:00:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:28</t>
+          <t>2026-09-29 01:00:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:28</t>
+          <t>2026-09-29 01:00:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:28</t>
+          <t>2026-09-29 01:00:35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:28</t>
+          <t>2026-09-29 01:00:35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 00:51:28</t>
+          <t>2026-09-29 01:00:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2475</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.93%5285</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.93%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5285</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.16%1185</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.16%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1185</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.6%5050</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>5050</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.45%3555</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.45%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3555</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+7.96%6920</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+7.96%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6920</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.22%580</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>580</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.53%1910</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.53%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1910</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.65%5415</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.65%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5415</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.75%154</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.75%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>154</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.26%1895</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.26%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1895</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.48%1240</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.48%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1240</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.48%2115</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2115</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.87%699</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.87%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>699</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:28</t>
+          <t>2026-09-29 01:39:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%2340</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2340</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:32</t>
+          <t>2026-09-29 01:39:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:34</t>
+          <t>2026-09-29 01:39:19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:00:35</t>
+          <t>2026-09-29 01:39:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.77%11,464,000</t>
+          <t>10.00%11,464,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.77%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.26%5,086,000</t>
+          <t>8.80%5,086,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.26%</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1185</v>
+        <v>1165</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.20%20,100,000</t>
+          <t>8.25%20,100,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.20%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.09%4,650,000</t>
+          <t>8.06%4,650,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.09%</t>
+          <t>8.06%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3555</v>
+        <v>3400</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.21%5,889,000</t>
+          <t>7.06%5,889,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.21%</t>
+          <t>7.06%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6920</v>
+        <v>6895</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.96%2,502,000</t>
+          <t>6.08%2,502,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.96%</t>
+          <t>6.08%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.22%580</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>580</v>
+        <v>1835</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.95%24,757,000</t>
+          <t>4.78%7,389,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>4.78%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>24757000</v>
+        <v>7389000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>-5.52%548</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1910</v>
+        <v>548</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.82%7,320,000</t>
+          <t>4.78%24,757,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.78%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7320000</v>
+        <v>24757000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-0.32%153.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5415</v>
+        <v>153.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.66%2,499,000</t>
+          <t>4.71%87,118,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>4.71%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2499000</v>
+        <v>87118000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>154</v>
+        <v>5185</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.62%87,118,000</t>
+          <t>4.57%2,499,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>4.57%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>87118000</v>
+        <v>2499000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1895</v>
+        <v>1270</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.09%6,264,000</t>
+          <t>4.00%8,937,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.09%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6264000</v>
+        <v>8937000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1240</v>
+        <v>1810</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.82%8,937,000</t>
+          <t>4.00%6,264,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>8937000</v>
+        <v>6264000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,33 +1241,33 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.55%4,873,561</t>
+          <t>3.56%4,812,561</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>4873561</v>
+        <v>4812561</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>699</v>
+        <v>2445</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.36%13,966,000</t>
+          <t>3.34%3,876,848</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.34%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>13966000</v>
+        <v>3876848</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:17</t>
+          <t>2026-09-29 22:54:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>-0.67%1485</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2340</v>
+        <v>1485</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.12%3,876,848</t>
+          <t>3.22%6,151,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>3876848</v>
+        <v>6151000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,40 +1419,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>687</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.03%5,886,000</t>
+          <t>3.14%12,966,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5886000</v>
+        <v>12966000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,27 +1487,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.69%2530</t>
+          <t>-0.59%2515</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.46%1,673,000</t>
+          <t>1.48%1,673,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,27 +1550,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+2.3%311</t>
+          <t>-5.31%294.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>294.5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.39%12,938,450</t>
+          <t>1.34%12,938,450</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>-2.22%19395</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>19395</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,27 +1676,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.67%8525</t>
+          <t>-7.04%7925</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-7.04%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.14%388,000</t>
+          <t>1.08%388,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,35 +1739,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.07%1105</t>
+          <t>+1.36%1120</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.62%1,634,000</t>
+          <t>0.80%2,022,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1634000</v>
+        <v>2022000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,27 +1802,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.53%475.5</t>
+          <t>+4.84%498.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+4.84%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>475.5</t>
+          <t>498.5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.57%3,483,000</t>
+          <t>0.61%3,483,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.38%246</t>
+          <t>-1.83%241.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>241.5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,17 +1928,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.56%897</t>
+          <t>-2.23%877</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>877</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1991,27 +1991,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.75%3310</t>
+          <t>-5.14%3140</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.29%251,000</t>
+          <t>0.28%251,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2054,27 +2054,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.65%1530</t>
+          <t>+3.59%1585</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>+3.59%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.25%476,000</t>
+          <t>0.27%476,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,31 +2117,31 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.44%212</t>
+          <t>+1.89%216</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>216</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.23%3,193,000</t>
+          <t>0.20%2,674,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3193000</v>
+        <v>2674000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.42%5850</t>
+          <t>-2.99%5675</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:18</t>
+          <t>2026-09-29 22:54:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2243,17 +2243,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.22%229</t>
+          <t>-0.87%227</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>227</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,16 +2306,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.6%82.3</t>
+          <t>+0.97%83.1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>82.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2367,25 +2367,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.42%174</t>
+          <t>-1.44%171.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>174</v>
+        <v>171.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.10%1,740,000</t>
+          <t>0.11%1,740,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2423,38 +2423,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.67%222.5</t>
+          <t>+9.62%1310</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+9.62%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>222.5</v>
+        <v>1310</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.04%501,000</t>
+          <t>0.06%121,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>501000</v>
+        <v>121000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2484,34 +2484,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2002中鋼</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0%18.65</t>
+          <t>+1.57%226</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>18.65</v>
+        <v>226</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.03%5,163,000</t>
+          <t>0.04%501,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>5163000</v>
+        <v>501000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2545,34 +2545,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.82%511</t>
+          <t>+0.8%18.8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.82%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>511</v>
+        <v>18.8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.03%5,163,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2606,21 +2606,21 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.27%3770</t>
+          <t>-2.54%498</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3770</v>
+        <v>498</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2667,21 +2667,21 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2439美律</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.26%78.2</t>
+          <t>-2.25%3685</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>78.2</v>
+        <v>3685</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2728,21 +2728,21 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>2439美律</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.63%1210</t>
+          <t>-0.13%78.1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1210</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2789,21 +2789,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>0%1210</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6245</v>
+        <v>1210</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2850,21 +2850,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.88%338.5</t>
+          <t>-3.6%6020</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>338.5</v>
+        <v>6020</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2911,21 +2911,21 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.83%1195</t>
+          <t>-0.59%336.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1195</v>
+        <v>336.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +2977,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-4.58%563</t>
+          <t>+0.71%567</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-4.58%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-2.33%503</t>
+          <t>+0.6%506</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3099,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%100.5</t>
+          <t>-5.47%95</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.47%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>100.5</v>
+        <v>95</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:19</t>
+          <t>2026-09-29 22:54:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3160,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2295</v>
+        <v>2185</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:21</t>
+          <t>2026-09-29 22:54:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,16 +3221,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.21%948</t>
+          <t>-0.32%945</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:21</t>
+          <t>2026-09-29 22:54:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3282,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.42%572</t>
+          <t>-0.52%569</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:21</t>
+          <t>2026-09-29 22:54:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+4.67%112</t>
+          <t>-6.7%104.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>112</v>
+        <v>104.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:21</t>
+          <t>2026-09-29 22:54:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.15%250.5</t>
+          <t>0%250.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:21</t>
+          <t>2026-09-29 22:54:29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3465,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.45%170.5</t>
+          <t>+4.69%178.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>170.5</v>
+        <v>178.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:39:21</t>
+          <t>2026-09-29 22:54:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.87%174.5</t>
+          <t>+0.57%175.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>174.5</v>
+        <v>175.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-29_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2475</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2475</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-7.1%4910</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>4910</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.69%1165</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.69%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1165</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.57%4920</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.57%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>4920</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-4.36%3400</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-4.36%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3400</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.36%6895</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.36%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>6895</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.93%1835</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.93%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1835</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.52%548</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.52%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>548</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.32%153.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.32%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>153.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-4.25%5185</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-4.25%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>5185</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.42%1270</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.42%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1270</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.49%1810</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.49%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1810</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.71%2100</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.71%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>2100</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.49%2445</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.49%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2445</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:25</t>
+          <t>2026-09-29 23:04:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.67%1485</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.67%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1485</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:27</t>
+          <t>2026-09-29 23:04:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:28</t>
+          <t>2026-09-29 23:04:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:29</t>
+          <t>2026-09-29 23:04:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:29</t>
+          <t>2026-09-29 23:04:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:29</t>
+          <t>2026-09-29 23:04:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:29</t>
+          <t>2026-09-29 23:04:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:29</t>
+          <t>2026-09-29 23:04:29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 22:54:29</t>
+          <t>2026-09-29 23:04:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2475</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-7.1%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>4910</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.69%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1165</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.57%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4920</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.36%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3400</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.36%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6895</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.93%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1835</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.52%548</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.52%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>548</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.32%153.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>153.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.25%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5185</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.42%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1270</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.49%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1810</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.71%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2100</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+4.49%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2445</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:18</t>
+          <t>2026-09-29 23:50:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.67%1485</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.67%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1485</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:27</t>
+          <t>2026-09-29 23:50:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:28</t>
+          <t>2026-09-29 23:50:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:29</t>
+          <t>2026-09-29 23:50:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:29</t>
+          <t>2026-09-29 23:50:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:29</t>
+          <t>2026-09-29 23:50:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:29</t>
+          <t>2026-09-29 23:50:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:29</t>
+          <t>2026-09-29 23:50:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 23:04:29</t>
+          <t>2026-09-29 23:50:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
